--- a/data/trans_orig/IP29_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP29_R-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>23474</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37635</t>
+          <t>37771</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,47 +747,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>26,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>27980</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21831</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35074</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>26,15%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>27980</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21867</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>34961</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>26,19%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48788</t>
+          <t>48545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68547</t>
+          <t>67810</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51120</t>
+          <t>50984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65550</t>
+          <t>65281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,49 +860,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>73,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>55507</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48413</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>61656</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>66,49%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>57,99%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>73,85%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>55507</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48526</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61620</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>66,49%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>58,12%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>73,81%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>171</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103695</t>
+          <t>104432</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123454</t>
+          <t>123697</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,82%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118721</t>
+          <t>119612</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147937</t>
+          <t>148651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108667</t>
+          <t>110191</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140685</t>
+          <t>139594</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>236462</t>
+          <t>237768</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>280024</t>
+          <t>278489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250123</t>
+          <t>249409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>279339</t>
+          <t>278448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>319172</t>
+          <t>320263</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>351190</t>
+          <t>349666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>577893</t>
+          <t>579428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>621455</t>
+          <t>620149</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,29%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>33275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>52187</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38868</t>
+          <t>37876</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56953</t>
+          <t>56842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75771</t>
+          <t>76741</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102740</t>
+          <t>103159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114818</t>
+          <t>113763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133025</t>
+          <t>132675</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94414</t>
+          <t>94525</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112499</t>
+          <t>113491</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>214577</t>
+          <t>214158</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>241546</t>
+          <t>240576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>187669</t>
+          <t>186301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>226564</t>
+          <t>225741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180742</t>
+          <t>180134</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>218377</t>
+          <t>218099</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>375757</t>
+          <t>379559</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>430980</t>
+          <t>431631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>426201</t>
+          <t>427024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>465096</t>
+          <t>466464</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>476334</t>
+          <t>476612</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>513969</t>
+          <t>514577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>916495</t>
+          <t>915844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>971718</t>
+          <t>967916</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>16089</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29287</t>
+          <t>29720</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16907</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>30393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36343</t>
+          <t>35623</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55481</t>
+          <t>55619</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61012</t>
+          <t>60579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74238</t>
+          <t>74210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51535</t>
+          <t>51593</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65079</t>
+          <t>65752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116804</t>
+          <t>116666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135942</t>
+          <t>136662</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102415</t>
+          <t>104451</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>132648</t>
+          <t>135023</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99980</t>
+          <t>100606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131565</t>
+          <t>131764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>213396</t>
+          <t>211771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>257124</t>
+          <t>256943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310307</t>
+          <t>307932</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>340540</t>
+          <t>338504</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351725</t>
+          <t>351526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>383310</t>
+          <t>382684</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>669121</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>712849</t>
+          <t>714474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37988</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57612</t>
+          <t>57265</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27085</t>
+          <t>27516</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44168</t>
+          <t>46165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68686</t>
+          <t>69375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96072</t>
+          <t>95257</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104335</t>
+          <t>104682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>123959</t>
+          <t>123554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123304</t>
+          <t>121307</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140387</t>
+          <t>139956</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>233348</t>
+          <t>234163</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>260734</t>
+          <t>260045</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170146</t>
+          <t>167710</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>207315</t>
+          <t>207091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153260</t>
+          <t>155226</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192415</t>
+          <t>193932</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>333657</t>
+          <t>333144</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>389299</t>
+          <t>388956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487886</t>
+          <t>488110</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>525055</t>
+          <t>527491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>540333</t>
+          <t>538816</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>579488</t>
+          <t>577522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1038650</t>
+          <t>1038993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1094292</t>
+          <t>1094805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>21470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21537</t>
+          <t>21422</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22935</t>
+          <t>23647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38572</t>
+          <t>39600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36329</t>
+          <t>36632</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47390</t>
+          <t>47650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45556</t>
+          <t>45671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56907</t>
+          <t>57578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86623</t>
+          <t>85595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102260</t>
+          <t>101548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116072</t>
+          <t>117328</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147746</t>
+          <t>149399</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>128523</t>
+          <t>129482</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161760</t>
+          <t>162398</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>255525</t>
+          <t>253457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>303089</t>
+          <t>300107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>313921</t>
+          <t>312268</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345595</t>
+          <t>344339</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317305</t>
+          <t>316667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>350542</t>
+          <t>349583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>637643</t>
+          <t>640625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>685207</t>
+          <t>687275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,06%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>42584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61851</t>
+          <t>62304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49679</t>
+          <t>50317</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70543</t>
+          <t>70521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98415</t>
+          <t>97816</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126657</t>
+          <t>126639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104719</t>
+          <t>104266</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124285</t>
+          <t>123986</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110444</t>
+          <t>110466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131308</t>
+          <t>130670</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220900</t>
+          <t>220918</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>249142</t>
+          <t>249741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181116</t>
+          <t>181939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>217984</t>
+          <t>218783</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201162</t>
+          <t>198247</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>240839</t>
+          <t>240145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,47 +5017,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>27,26%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>33,03%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>420535</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>390945</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>448340</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>29,75%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>27,66%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>33,12%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>420535</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>391273</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>448977</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>29,75%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>468355</t>
+          <t>467556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>505223</t>
+          <t>504400</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>486306</t>
+          <t>487000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>525983</t>
+          <t>528898</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,47 +5130,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>72,74%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>992949</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>965144</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1022539</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>70,25%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>68,28%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>72,34%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1464</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>992949</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>964507</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1022211</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>70,25%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>68,24%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>72,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP29_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP29_R-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27980</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20703</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35001</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>41,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>30280</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23474</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37771</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23519</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>37687</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>34,12%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>27980</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21831</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>35074</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48545</t>
+          <t>49160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67810</t>
+          <t>68649</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55507</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48486</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>62784</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>58,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>58475</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50984</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>65281</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>51068</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>65236</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>65,88%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>73,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>55507</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48413</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61656</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>66,49%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104432</t>
+          <t>103593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123697</t>
+          <t>123082</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,46%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83487</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83487</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83487</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88755</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88755</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88755</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83487</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83487</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83487</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>123507</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>109598</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>137642</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,83%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>133029</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>119612</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>148651</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>117890</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>148175</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>33,42%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,05%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>37,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>123507</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>110191</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>139594</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>237768</t>
+          <t>235286</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>278489</t>
+          <t>278555</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>336350</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>322215</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>350259</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>73,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>401</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>265031</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>249409</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>278448</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>249885</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>280170</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>66,58%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,95%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>336350</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>320263</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>349666</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>73,14%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>579428</t>
+          <t>579362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>620149</t>
+          <t>622631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,57%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>459857</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>459857</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>459857</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>602</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>398060</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>398060</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>398060</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>459857</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>459857</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>459857</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47348</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>38518</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>57990</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>41790</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33275</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>52187</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>33195</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>51597</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>25,18%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,45%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>47348</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>37876</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>56842</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>31,28%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76741</t>
+          <t>75918</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103159</t>
+          <t>102979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>104019</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>93377</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>112849</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>68,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>61,69%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>74,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>124160</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>113763</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>132675</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>114353</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>132755</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>74,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>68,55%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>79,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>104019</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>94525</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>113491</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>68,72%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>214158</t>
+          <t>214338</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240576</t>
+          <t>241399</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>151367</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>151367</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>151367</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165950</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165950</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165950</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>151367</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>151367</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>151367</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>198835</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>181354</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>218578</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>28,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>205100</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>186301</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>225741</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>186056</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>223047</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>31,42%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,54%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>198835</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>180134</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>218099</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>28,62%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>379559</t>
+          <t>379147</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>431631</t>
+          <t>435261</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>495876</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>476133</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>513357</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>71,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>671</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>447665</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>427024</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>466464</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>429718</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>466709</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>68,58%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>495876</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>476612</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>514577</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>915844</t>
+          <t>912214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>967916</t>
+          <t>968328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>694711</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>694711</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>694711</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>977</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>652765</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>652765</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>652765</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>694711</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>694711</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>694711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,72 +2325,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22866</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16849</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30555</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>37,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>22301</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16089</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29720</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16116</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29927</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>24,7%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,82%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>22866</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>16234</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>30393</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35623</t>
+          <t>35829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55619</t>
+          <t>55331</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -2438,72 +2438,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59120</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51431</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>65137</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>72,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>62,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>67998</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>60579</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>74210</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>60372</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>74183</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>75,3%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,09%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,18%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59120</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51593</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>65752</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>72,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116666</t>
+          <t>116954</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136662</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81986</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81986</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81986</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90299</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90299</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90299</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>81986</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>81986</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>81986</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>115453</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>100864</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>132825</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>20,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>118400</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>104451</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>135023</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>102563</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>133893</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>26,73%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>23,58%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>30,48%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>115453</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>100606</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>131764</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>211771</t>
+          <t>210506</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>256943</t>
+          <t>254932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>367837</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>350465</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>382426</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>470</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>324555</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>307932</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>338504</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>309062</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>340392</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>73,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>367837</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>351526</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>382684</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>671313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>714474</t>
+          <t>715739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>483290</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>483290</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>483290</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>442955</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>442955</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>442955</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>483290</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>483290</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>483290</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35523</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27263</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>46561</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>47209</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>38393</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>57265</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>38565</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>58136</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,15%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>35523</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>27516</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>46165</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69375</t>
+          <t>69793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95257</t>
+          <t>96925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>131949</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>120911</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>140209</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>72,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>83,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>114738</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>104682</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>123554</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>103811</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>123382</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>70,85%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>64,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,29%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>131949</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>121307</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>139956</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>78,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>234163</t>
+          <t>232495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>260045</t>
+          <t>259627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167472</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167472</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167472</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>161947</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>161947</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>161947</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>167472</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>167472</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>167472</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>173843</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>154210</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>192899</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,72%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,05%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>187911</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>167710</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>207091</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>167451</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>205543</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>27,03%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>173843</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>155226</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>193932</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>23,72%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>333144</t>
+          <t>334744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>388956</t>
+          <t>391190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>558905</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>539849</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>578538</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>76,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>78,95%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>732</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>507290</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>488110</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>527491</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>489658</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>527750</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>72,97%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>75,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>558905</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>538816</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>577522</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>76,28%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1038993</t>
+          <t>1036759</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1094805</t>
+          <t>1093205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,56%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>732748</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>732748</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>732748</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>695201</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>695201</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>695201</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1046</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>732748</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>732748</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>732748</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,72 +3928,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10021</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20991</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15588</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10452</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21470</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10439</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21054</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>26,83%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15026</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9515</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21422</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>22,4%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39600</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52067</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46102</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>57072</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>77,6%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>42514</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>36632</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>47650</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>37048</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>47663</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>73,17%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>63,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>52067</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>45671</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>57578</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>77,6%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85595</t>
+          <t>86689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101548</t>
+          <t>102101</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58102</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58102</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58102</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>67093</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>67093</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>67093</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>145935</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>129053</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>162804</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,94%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>132164</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>117328</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>149399</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>116908</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>147949</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>28,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>25,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,36%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>145935</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>129482</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>162398</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>30,46%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>253457</t>
+          <t>253376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>300107</t>
+          <t>301292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>333130</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>316261</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>350012</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>69,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>66,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73,06%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>329503</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>312268</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>344339</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>313718</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>344759</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>71,37%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>333130</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>316667</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>349583</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>69,54%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>640625</t>
+          <t>639440</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>687275</t>
+          <t>687356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,07%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>479065</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>479065</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>479065</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>698</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>461667</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>461667</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>461667</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>479065</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>479065</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>479065</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,72 +4614,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59793</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50398</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>71281</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>39,38%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>42584</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>62304</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>42892</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>61835</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>31,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>59793</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>50317</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>70521</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>33,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97816</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126639</t>
+          <t>126127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -4727,72 +4727,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>121194</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>109706</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>130589</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>66,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>60,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>114541</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>104266</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>123986</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>104735</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>123678</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>68,76%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>74,44%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>121194</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>110466</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>130670</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>66,96%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220918</t>
+          <t>221430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>249741</t>
+          <t>249512</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>180987</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>180987</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>180987</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166570</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166570</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166570</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>180987</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>180987</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>180987</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>220754</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>200495</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>243531</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>30,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>301</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>199781</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>181939</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>218783</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>181532</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>220370</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>29,11%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26,51%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>220754</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>198247</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>240145</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>390945</t>
+          <t>393370</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>448340</t>
+          <t>449071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>506391</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>483614</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>526650</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>69,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66,51%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>486558</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>467556</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>504400</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>465969</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>504807</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>70,89%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>73,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>506391</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>487000</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>528898</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>69,64%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>965144</t>
+          <t>964413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1022539</t>
+          <t>1020114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,17%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>727145</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>727145</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>727145</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1034</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>686339</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>686339</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>686339</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>727145</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>727145</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>727145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
